--- a/public/templates/manifesto-bb-modelo.xlsx
+++ b/public/templates/manifesto-bb-modelo.xlsx
@@ -397,37 +397,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:I2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>BL</v>
       </c>
       <c r="B1" t="str">
-        <v>CE</v>
+        <v>MAQUINAS</v>
       </c>
       <c r="C1" t="str">
-        <v>MAQUINAS</v>
+        <v>PACKAGES</v>
       </c>
       <c r="D1" t="str">
-        <v>PACKAGES</v>
+        <v>PACKAGES TOTAL</v>
       </c>
       <c r="E1" t="str">
-        <v>PACKAGES TOTAL</v>
+        <v>WEIGHT (TON)</v>
       </c>
       <c r="F1" t="str">
-        <v>WEIGHT (TON)</v>
+        <v>CBM (M3)</v>
       </c>
       <c r="G1" t="str">
-        <v>CBM (M3)</v>
+        <v>SHIPPER</v>
       </c>
       <c r="H1" t="str">
-        <v>SHIPPER</v>
+        <v>CONSIGNEE</v>
       </c>
       <c r="I1" t="str">
-        <v>CONSIGNEE</v>
-      </c>
-      <c r="J1" t="str">
         <v>NOTIFY</v>
       </c>
     </row>
@@ -436,36 +433,33 @@
         <v>BL-EXEMPLO</v>
       </c>
       <c r="B2">
-        <v>122605051526081</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>12.5</v>
       </c>
       <c r="F2">
-        <v>12.5</v>
-      </c>
-      <c r="G2">
         <v>34.8</v>
       </c>
+      <c r="G2" t="str">
+        <v>EMBARCADOR EXEMPLO</v>
+      </c>
       <c r="H2" t="str">
-        <v>EMBARCADOR EXEMPLO</v>
+        <v>CONSIGNATARIO EXEMPLO</v>
       </c>
       <c r="I2" t="str">
-        <v>CONSIGNATARIO EXEMPLO</v>
-      </c>
-      <c r="J2" t="str">
         <v>NOTIFY EXEMPLO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
   </ignoredErrors>
 </worksheet>
 </file>